--- a/assets/VER_Training_Input_Form.xlsx
+++ b/assets/VER_Training_Input_Form.xlsx
@@ -1,58 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="READ ME FIRST" sheetId="1" r:id="rId1"/>
-    <sheet name="1. Header" sheetId="2" r:id="rId2"/>
-    <sheet name="2. Objectives" sheetId="3" r:id="rId3"/>
-    <sheet name="3. Coverage" sheetId="4" r:id="rId4"/>
-    <sheet name="4. Results" sheetId="5" r:id="rId5"/>
-    <sheet name="5. Next Steps" sheetId="6" r:id="rId6"/>
-    <sheet name="6. Custom Notes" sheetId="7" r:id="rId7"/>
+    <sheet name="READ ME FIRST" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1. Header" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2. Objectives" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3. Coverage" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="4. Results" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="5. Next Steps" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="6. Custom Notes" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -71,13 +48,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -402,332 +446,666 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>VER TRAINING &amp; ENABLEMENT INPUT FORM</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v/>
-      </c>
-    </row>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>VER TRAINING &amp; ENABLEMENT INPUT FORM</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" t="str">
-        <v>INSTRUCTIONS</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>INSTRUCTIONS</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>Fill in each tab with your meeting data.</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Fill in each tab with your meeting data.</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>All fields are optional — fill what you have.</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>All fields are optional — fill what you have.</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>Return this file to VER or paste values into the generator.</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Return this file to VER or paste values into the generator.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A6"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Field</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Value</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Session Title</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Session Title</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>VER Intelligence Hub — Analyst Enablement Workshop</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>Date</v>
-      </c>
-      <c r="B3" t="str">
-        <v/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>Facilitator</v>
-      </c>
-      <c r="B4" t="str">
-        <v/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Facilitator</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Casey Candelaria</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>Audience</v>
-      </c>
-      <c r="B5" t="str">
-        <v/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Audience</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VER Intelligence Team, DET Delivery Assurance Analysts</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>Duration</v>
-      </c>
-      <c r="B6" t="str">
-        <v/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>N/A — Internal VER Training</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>Format</v>
-      </c>
-      <c r="B7" t="str">
-        <v/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FY / Period</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FY27 Q1</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>#</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Objective</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Status</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Objective</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>1</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Analysts can generate and customize a full cinematic CQBR using the generator</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Team understands how to map Excel inputs to each cinematic scene</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Team can interpret By the Numbers, health scorecard, and timeline outputs for stakeholders</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>All analysts know the Add to Library workflow and how CQBR records persist</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rate benchmark interpretation and usage in renewal prep is covered</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Topic</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Depth</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Notes</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Depth</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v/>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Generator Overview — all 9 presentation types</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Deep</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Live demo with Cognizant CQBR as reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Excel Input Form walkthrough — all 10 CQBR sheets</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Deep</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Each tab explained with field-level guidance</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Scene anatomy — By the Numbers, Timeline, Health, Innovation</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Deep</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Screenshot annotations of each scene</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Flash / Core / Apex tier differences</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>When to use each tier for different audiences</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CQBR Library — Add to Library, search, filter</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Deep</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Hands-on exercise: each analyst generates and saves a record</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Rate Benchmark tab — interpretation and negotiation use</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Two worked examples from recent renewals</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Metric</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Target</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Actual</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Attendance</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>Completion Rate</v>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Completion Rate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>Quiz Score</v>
-      </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Knowledge Check Score</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Hands-On Exercise Completion</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Post-Session Satisfaction</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>9/10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>9.2/10</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>#</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Action</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Due</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Due</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>1</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Each analyst generates their assigned Q1 CQBR within 5 business days</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>VER Team</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Casey to record short walkthrough video for onboarding new analysts</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Casey Candelaria</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Add rate benchmark interpretation module to next session</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Casey Candelaria</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Label</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Notes</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v/>
-      </c>
-      <c r="B2" t="str">
-        <v/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Feedback Themes</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Team loved the cinematic format. Most common question: how do we handle vendors who submit incomplete Excel files? Action: add validation guidance to template.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tool Readiness</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>All 8 analysts confirmed able to generate independently after workshop. 2 requested follow-up on Excel field mapping for attrition data.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>